--- a/engine/egch_study/EGCH_Valuation_Model_03092026.xlsx
+++ b/engine/egch_study/EGCH_Valuation_Model_03092026.xlsx
@@ -6247,7 +6247,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" ht="72" customHeight="1">
+    <row r="111" ht="108" customHeight="1">
       <c r="A111" s="6" t="inlineStr">
         <is>
           <t>Terminal inflation (the same figure terminal growth is set at)</t>
@@ -6263,7 +6263,7 @@
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>The inflation embedded in the TERMINAL discount rate: the central bank's longest-horizon published target, 5% (+/-2) for Q4 2028 — the SAME figure terminal growth is set at. CORRECTED 1 September 2026: the 08-08-2026 edition built the terminal risk-free rate on the 7% Q4-2026 target while growing the perpetuity at 5%, a perpetual real decline of about 2% a year that no disclosure supports (the same defect the AMOC review found, L-055). Terminal growth, the terminal risk-free rate and the terminal currency wedge now share one inflation.</t>
+          <t>The inflation embedded in the TERMINAL discount rate, taken from the house macro path and NOT typed here — the SAME figure terminal growth is set at, so the two cannot drift apart. (This sentence previously described the value as 5%, the central bank's Q4-2028 target, while the path supplies 7%: a 7% value carrying a 5% justification, which is exactly the kind of unfalsifiable typed rate [R-MACRO-01] exists to stop. The value has always come from the path; only the sentence was wrong.) CORRECTED 1 September 2026: the 08-08-2026 edition built the terminal risk-free rate on the 7% Q4-2026 target while growing the perpetuity at 5%, a perpetual real decline of about 2% a year that no disclosure supports (the same defect the AMOC review found, L-055). Terminal growth, the terminal risk-free rate and the terminal currency wedge now share one inflation.</t>
         </is>
       </c>
     </row>

--- a/engine/egch_study/EGCH_Valuation_Model_03092026.xlsx
+++ b/engine/egch_study/EGCH_Valuation_Model_03092026.xlsx
@@ -2675,19 +2675,19 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>-2.64</v>
+        <v>-2.49</v>
       </c>
       <c r="C6" s="12" t="n">
+        <v>-2.63</v>
+      </c>
+      <c r="D6" s="12" t="n">
         <v>-2.76</v>
       </c>
-      <c r="D6" s="12" t="n">
-        <v>-2.88</v>
-      </c>
       <c r="E6" s="12" t="n">
-        <v>-2.95</v>
+        <v>-2.84</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>-3.02</v>
+        <v>-2.92</v>
       </c>
     </row>
     <row r="7">
@@ -2697,19 +2697,19 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>-1.08</v>
+        <v>-0.8</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>-1.3</v>
+        <v>-1.05</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>-1.51</v>
+        <v>-1.29</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>-1.65</v>
+        <v>-1.44</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>-1.78</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="8">
@@ -2719,19 +2719,19 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.49</v>
+        <v>0.89</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>0.16</v>
+        <v>0.53</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>-0.14</v>
+        <v>0.19</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>-0.34</v>
+        <v>-0.03</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>-0.53</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="9">
@@ -2741,19 +2741,19 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>2.05</v>
+        <v>2.57</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>1.63</v>
+        <v>2.1</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>1.23</v>
+        <v>1.66</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>0.97</v>
+        <v>1.38</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>0.71</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="10">
@@ -2763,19 +2763,19 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>3.61</v>
+        <v>4.26</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>3.09</v>
+        <v>3.68</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>2.59</v>
+        <v>3.14</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>2.27</v>
+        <v>2.78</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1.96</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="13" ht="52" customHeight="1">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>1.785377453868092</v>
+        <v>2.310891559889441</v>
       </c>
       <c r="D17" s="11">
         <f>C17-$D$15</f>
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>0.3670158141445878</v>
+        <v>0.5729787587400788</v>
       </c>
       <c r="D18" s="11">
         <f>C18-$D$15</f>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>1.681839374144488</v>
+        <v>2.199529451608678</v>
       </c>
       <c r="D19" s="11">
         <f>C19-$D$15</f>
@@ -2883,7 +2883,7 @@
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>The cost of debt at the company's own disclosed rates — 19.4% on the local facility, 11.7% in dollars on the project loan carried at local-equivalent cost on the derived currency path, 20.0% in year one gliding to 13.9% at the terminal</t>
+          <t>The cost of debt at the company's own disclosed rates — 19.4% on the local facility, 11.7% in dollars on the project loan carried at local-equivalent cost on the derived currency path, 24.4% in year one gliding to 13.9% at the terminal</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -2892,7 +2892,7 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>0.9828446765320163</v>
+        <v>1.535325976274551</v>
       </c>
       <c r="D20" s="11">
         <f>C20-$D$15</f>
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>2.859085724910241</v>
+        <v>3.498713152528789</v>
       </c>
       <c r="D21" s="11">
         <f>C21-$D$15</f>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>-0.1265904861401076</v>
+        <v>0.2460834508623395</v>
       </c>
       <c r="D22" s="11">
         <f>C22-$D$15</f>
@@ -2949,7 +2949,7 @@
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>2.015514431643158</v>
+        <v>2.564332955202137</v>
       </c>
       <c r="D23" s="11">
         <f>C23-$D$15</f>
@@ -2968,7 +2968,7 @@
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>0.9216105075155367</v>
+        <v>1.403708461239366</v>
       </c>
       <c r="D24" s="11">
         <f>C24-$D$15</f>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>2.624416745702623</v>
+        <v>3.239589266110914</v>
       </c>
       <c r="D25" s="11">
         <f>C25-$D$15</f>
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="C26" s="12" t="n">
-        <v>1.552597382184459</v>
+        <v>2.079574021395053</v>
       </c>
       <c r="D26" s="11">
         <f>C26-$D$15</f>
@@ -3720,7 +3720,7 @@
         </is>
       </c>
       <c r="B25" s="15" t="n">
-        <v>0.1096361607961464</v>
+        <v>0.1150130180266282</v>
       </c>
     </row>
     <row r="26">
@@ -3805,7 +3805,7 @@
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>5.900148689005042</v>
+        <v>6.259070497380644</v>
       </c>
     </row>
     <row r="37">
@@ -3826,7 +3826,7 @@
         </is>
       </c>
       <c r="B38" s="12" t="n">
-        <v>4.756234842977872</v>
+        <v>5.095373540542885</v>
       </c>
     </row>
     <row r="39">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>1.785377453868092</v>
+        <v>2.310891559889441</v>
       </c>
     </row>
     <row r="24">
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>5.900148689005042</v>
+        <v>6.259070497380644</v>
       </c>
     </row>
     <row r="25">
@@ -4174,7 +4174,7 @@
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>15.4744443192992</v>
+        <v>15.98773106857623</v>
       </c>
     </row>
     <row r="27">
@@ -5763,7 +5763,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="48" customHeight="1">
+    <row r="84" ht="84" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
         <is>
           <t>Egyptian inflation — FY2026/27</t>
@@ -5775,15 +5775,15 @@
         </is>
       </c>
       <c r="C84" s="15" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Domestic inflation converging from the June 2026 print (14.3%) on the central bank's own target ladder: 7% (+/-2) for Q4 2026, which falls in FY2026/27-FY2027/28, and 5% (+/-2) for Q4 2028, which falls in FY2028/29, held thereafter. RE-SET 1 September 2026 so that the explicit path lands on the terminal inflation rather than stepping down to it at the terminal boundary.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="48" customHeight="1">
+          <t>DERIVED from the house macro path for Egypt (engine/macro_paths/EG.json, as of 2026-09-02), mapped onto this company's 30 June fiscal year end: each fiscal year takes half of each of the two calendar years it spans, and beyond the ladder's last published year the house terminal inflation. The house ladder is 2026 16.0% / 2027 12.0% / 2028 9.0% / 2029 7.5% / 2030 7.0%. No number here is chosen by this study: under [R-MACRO-01] a study may not carry an inflation number of its own, and until 3 September 2026 this array was typed at 10.0 / 7.0 / 6.0 / 5.0 / 5.0 — terminating at 5% while this study's own macro record already carried the house terminal of 7%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="84" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
         <is>
           <t>Egyptian inflation — FY2027/28</t>
@@ -5795,71 +5795,71 @@
         </is>
       </c>
       <c r="C85" s="15" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>DERIVED from the house macro path for Egypt (engine/macro_paths/EG.json, as of 2026-09-02), mapped onto this company's 30 June fiscal year end: each fiscal year takes half of each of the two calendar years it spans, and beyond the ladder's last published year the house terminal inflation. The house ladder is 2026 16.0% / 2027 12.0% / 2028 9.0% / 2029 7.5% / 2030 7.0%. No number here is chosen by this study: under [R-MACRO-01] a study may not carry an inflation number of its own, and until 3 September 2026 this array was typed at 10.0 / 7.0 / 6.0 / 5.0 / 5.0 — terminating at 5% while this study's own macro record already carried the house terminal of 7%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="84" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>Egyptian inflation — FY2028/29</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C86" s="15" t="n">
+        <v>0.08249999999999999</v>
+      </c>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>DERIVED from the house macro path for Egypt (engine/macro_paths/EG.json, as of 2026-09-02), mapped onto this company's 30 June fiscal year end: each fiscal year takes half of each of the two calendar years it spans, and beyond the ladder's last published year the house terminal inflation. The house ladder is 2026 16.0% / 2027 12.0% / 2028 9.0% / 2029 7.5% / 2030 7.0%. No number here is chosen by this study: under [R-MACRO-01] a study may not carry an inflation number of its own, and until 3 September 2026 this array was typed at 10.0 / 7.0 / 6.0 / 5.0 / 5.0 — terminating at 5% while this study's own macro record already carried the house terminal of 7%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="84" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>Egyptian inflation — FY2029/30</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C87" s="15" t="n">
+        <v>0.07250000000000001</v>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>DERIVED from the house macro path for Egypt (engine/macro_paths/EG.json, as of 2026-09-02), mapped onto this company's 30 June fiscal year end: each fiscal year takes half of each of the two calendar years it spans, and beyond the ladder's last published year the house terminal inflation. The house ladder is 2026 16.0% / 2027 12.0% / 2028 9.0% / 2029 7.5% / 2030 7.0%. No number here is chosen by this study: under [R-MACRO-01] a study may not carry an inflation number of its own, and until 3 September 2026 this array was typed at 10.0 / 7.0 / 6.0 / 5.0 / 5.0 — terminating at 5% while this study's own macro record already carried the house terminal of 7%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="84" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>Egyptian inflation — FY2030/31</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C88" s="15" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="D85" s="9" t="inlineStr">
-        <is>
-          <t>Domestic inflation converging from the June 2026 print (14.3%) on the central bank's own target ladder: 7% (+/-2) for Q4 2026, which falls in FY2026/27-FY2027/28, and 5% (+/-2) for Q4 2028, which falls in FY2028/29, held thereafter. RE-SET 1 September 2026 so that the explicit path lands on the terminal inflation rather than stepping down to it at the terminal boundary.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="48" customHeight="1">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>Egyptian inflation — FY2028/29</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C86" s="15" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="D86" s="9" t="inlineStr">
-        <is>
-          <t>Domestic inflation converging from the June 2026 print (14.3%) on the central bank's own target ladder: 7% (+/-2) for Q4 2026, which falls in FY2026/27-FY2027/28, and 5% (+/-2) for Q4 2028, which falls in FY2028/29, held thereafter. RE-SET 1 September 2026 so that the explicit path lands on the terminal inflation rather than stepping down to it at the terminal boundary.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="48" customHeight="1">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>Egyptian inflation — FY2029/30</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C87" s="15" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D87" s="9" t="inlineStr">
-        <is>
-          <t>Domestic inflation converging from the June 2026 print (14.3%) on the central bank's own target ladder: 7% (+/-2) for Q4 2026, which falls in FY2026/27-FY2027/28, and 5% (+/-2) for Q4 2028, which falls in FY2028/29, held thereafter. RE-SET 1 September 2026 so that the explicit path lands on the terminal inflation rather than stepping down to it at the terminal boundary.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="48" customHeight="1">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>Egyptian inflation — FY2030/31</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C88" s="15" t="n">
-        <v>0.05</v>
-      </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Domestic inflation converging from the June 2026 print (14.3%) on the central bank's own target ladder: 7% (+/-2) for Q4 2026, which falls in FY2026/27-FY2027/28, and 5% (+/-2) for Q4 2028, which falls in FY2028/29, held thereafter. RE-SET 1 September 2026 so that the explicit path lands on the terminal inflation rather than stepping down to it at the terminal boundary.</t>
+          <t>DERIVED from the house macro path for Egypt (engine/macro_paths/EG.json, as of 2026-09-02), mapped onto this company's 30 June fiscal year end: each fiscal year takes half of each of the two calendar years it spans, and beyond the ladder's last published year the house terminal inflation. The house ladder is 2026 16.0% / 2027 12.0% / 2028 9.0% / 2029 7.5% / 2030 7.0%. No number here is chosen by this study: under [R-MACRO-01] a study may not carry an inflation number of its own, and until 3 September 2026 this array was typed at 10.0 / 7.0 / 6.0 / 5.0 / 5.0 — terminating at 5% while this study's own macro record already carried the house terminal of 7%.</t>
         </is>
       </c>
     </row>

--- a/engine/egch_study/EGCH_Valuation_Model_03092026.xlsx
+++ b/engine/egch_study/EGCH_Valuation_Model_03092026.xlsx
@@ -5763,7 +5763,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="84" customHeight="1">
+    <row r="84" ht="96" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
         <is>
           <t>Egyptian inflation — FY2026/27</t>
@@ -5779,11 +5779,11 @@
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>DERIVED from the house macro path for Egypt (engine/macro_paths/EG.json, as of 2026-09-02), mapped onto this company's 30 June fiscal year end: each fiscal year takes half of each of the two calendar years it spans, and beyond the ladder's last published year the house terminal inflation. The house ladder is 2026 16.0% / 2027 12.0% / 2028 9.0% / 2029 7.5% / 2030 7.0%. No number here is chosen by this study: under [R-MACRO-01] a study may not carry an inflation number of its own, and until 3 September 2026 this array was typed at 10.0 / 7.0 / 6.0 / 5.0 / 5.0 — terminating at 5% while this study's own macro record already carried the house terminal of 7%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="84" customHeight="1">
+          <t>DERIVED from the single Egyptian inflation path this series uses for every Egyptian company it values (as of 2026-09-02), mapped onto this company's 30 June fiscal year end: each fiscal year takes half of each of the two calendar years it spans, and beyond the path's last published year its long-run rate. That path is 2026 16.0% / 2027 12.0% / 2028 9.0% / 2029 7.5% / 2030 7.0%. No number here is chosen for this study: a company cannot be valued in an economy the study beside it does not recognise, so no valuation in this series sets an inflation rate of its own. Until 3 September 2026 this array read 10.0 / 7.0 / 6.0 / 5.0 / 5.0 and ended at 5% while the same study already took 7% as the long-run rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="96" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
         <is>
           <t>Egyptian inflation — FY2027/28</t>
@@ -5799,11 +5799,11 @@
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>DERIVED from the house macro path for Egypt (engine/macro_paths/EG.json, as of 2026-09-02), mapped onto this company's 30 June fiscal year end: each fiscal year takes half of each of the two calendar years it spans, and beyond the ladder's last published year the house terminal inflation. The house ladder is 2026 16.0% / 2027 12.0% / 2028 9.0% / 2029 7.5% / 2030 7.0%. No number here is chosen by this study: under [R-MACRO-01] a study may not carry an inflation number of its own, and until 3 September 2026 this array was typed at 10.0 / 7.0 / 6.0 / 5.0 / 5.0 — terminating at 5% while this study's own macro record already carried the house terminal of 7%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="84" customHeight="1">
+          <t>DERIVED from the single Egyptian inflation path this series uses for every Egyptian company it values (as of 2026-09-02), mapped onto this company's 30 June fiscal year end: each fiscal year takes half of each of the two calendar years it spans, and beyond the path's last published year its long-run rate. That path is 2026 16.0% / 2027 12.0% / 2028 9.0% / 2029 7.5% / 2030 7.0%. No number here is chosen for this study: a company cannot be valued in an economy the study beside it does not recognise, so no valuation in this series sets an inflation rate of its own. Until 3 September 2026 this array read 10.0 / 7.0 / 6.0 / 5.0 / 5.0 and ended at 5% while the same study already took 7% as the long-run rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="96" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
         <is>
           <t>Egyptian inflation — FY2028/29</t>
@@ -5819,11 +5819,11 @@
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>DERIVED from the house macro path for Egypt (engine/macro_paths/EG.json, as of 2026-09-02), mapped onto this company's 30 June fiscal year end: each fiscal year takes half of each of the two calendar years it spans, and beyond the ladder's last published year the house terminal inflation. The house ladder is 2026 16.0% / 2027 12.0% / 2028 9.0% / 2029 7.5% / 2030 7.0%. No number here is chosen by this study: under [R-MACRO-01] a study may not carry an inflation number of its own, and until 3 September 2026 this array was typed at 10.0 / 7.0 / 6.0 / 5.0 / 5.0 — terminating at 5% while this study's own macro record already carried the house terminal of 7%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="84" customHeight="1">
+          <t>DERIVED from the single Egyptian inflation path this series uses for every Egyptian company it values (as of 2026-09-02), mapped onto this company's 30 June fiscal year end: each fiscal year takes half of each of the two calendar years it spans, and beyond the path's last published year its long-run rate. That path is 2026 16.0% / 2027 12.0% / 2028 9.0% / 2029 7.5% / 2030 7.0%. No number here is chosen for this study: a company cannot be valued in an economy the study beside it does not recognise, so no valuation in this series sets an inflation rate of its own. Until 3 September 2026 this array read 10.0 / 7.0 / 6.0 / 5.0 / 5.0 and ended at 5% while the same study already took 7% as the long-run rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="96" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
         <is>
           <t>Egyptian inflation — FY2029/30</t>
@@ -5839,11 +5839,11 @@
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>DERIVED from the house macro path for Egypt (engine/macro_paths/EG.json, as of 2026-09-02), mapped onto this company's 30 June fiscal year end: each fiscal year takes half of each of the two calendar years it spans, and beyond the ladder's last published year the house terminal inflation. The house ladder is 2026 16.0% / 2027 12.0% / 2028 9.0% / 2029 7.5% / 2030 7.0%. No number here is chosen by this study: under [R-MACRO-01] a study may not carry an inflation number of its own, and until 3 September 2026 this array was typed at 10.0 / 7.0 / 6.0 / 5.0 / 5.0 — terminating at 5% while this study's own macro record already carried the house terminal of 7%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="84" customHeight="1">
+          <t>DERIVED from the single Egyptian inflation path this series uses for every Egyptian company it values (as of 2026-09-02), mapped onto this company's 30 June fiscal year end: each fiscal year takes half of each of the two calendar years it spans, and beyond the path's last published year its long-run rate. That path is 2026 16.0% / 2027 12.0% / 2028 9.0% / 2029 7.5% / 2030 7.0%. No number here is chosen for this study: a company cannot be valued in an economy the study beside it does not recognise, so no valuation in this series sets an inflation rate of its own. Until 3 September 2026 this array read 10.0 / 7.0 / 6.0 / 5.0 / 5.0 and ended at 5% while the same study already took 7% as the long-run rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="96" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
         <is>
           <t>Egyptian inflation — FY2030/31</t>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>DERIVED from the house macro path for Egypt (engine/macro_paths/EG.json, as of 2026-09-02), mapped onto this company's 30 June fiscal year end: each fiscal year takes half of each of the two calendar years it spans, and beyond the ladder's last published year the house terminal inflation. The house ladder is 2026 16.0% / 2027 12.0% / 2028 9.0% / 2029 7.5% / 2030 7.0%. No number here is chosen by this study: under [R-MACRO-01] a study may not carry an inflation number of its own, and until 3 September 2026 this array was typed at 10.0 / 7.0 / 6.0 / 5.0 / 5.0 — terminating at 5% while this study's own macro record already carried the house terminal of 7%.</t>
+          <t>DERIVED from the single Egyptian inflation path this series uses for every Egyptian company it values (as of 2026-09-02), mapped onto this company's 30 June fiscal year end: each fiscal year takes half of each of the two calendar years it spans, and beyond the path's last published year its long-run rate. That path is 2026 16.0% / 2027 12.0% / 2028 9.0% / 2029 7.5% / 2030 7.0%. No number here is chosen for this study: a company cannot be valued in an economy the study beside it does not recognise, so no valuation in this series sets an inflation rate of its own. Until 3 September 2026 this array read 10.0 / 7.0 / 6.0 / 5.0 / 5.0 and ended at 5% while the same study already took 7% as the long-run rate.</t>
         </is>
       </c>
     </row>
@@ -6263,7 +6263,7 @@
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>The inflation embedded in the TERMINAL discount rate, taken from the house macro path and NOT typed here — the SAME figure terminal growth is set at, so the two cannot drift apart. (This sentence previously described the value as 5%, the central bank's Q4-2028 target, while the path supplies 7%: a 7% value carrying a 5% justification, which is exactly the kind of unfalsifiable typed rate [R-MACRO-01] exists to stop. The value has always come from the path; only the sentence was wrong.) CORRECTED 1 September 2026: the 08-08-2026 edition built the terminal risk-free rate on the 7% Q4-2026 target while growing the perpetuity at 5%, a perpetual real decline of about 2% a year that no disclosure supports (the same defect the AMOC review found, L-055). Terminal growth, the terminal risk-free rate and the terminal currency wedge now share one inflation.</t>
+          <t>The inflation embedded in the TERMINAL discount rate, taken from the house macro path and NOT typed here — the SAME figure terminal growth is set at, so the two cannot drift apart. (This sentence previously described the value as 5%, the central bank's Q4-2028 target, while the path supplies 7%: a 7% value carrying a 5% justification, which is exactly the kind of unfalsifiable typed rate this series does not permit. The value has always come from the path; only the sentence was wrong.) CORRECTED 1 September 2026: the 08-08-2026 edition built the terminal risk-free rate on the 7% Q4-2026 target while growing the perpetuity at 5%, a perpetual real decline of about 2% a year that no disclosure supports (the same defect the AMOC review found, L-055). Terminal growth, the terminal risk-free rate and the terminal currency wedge now share one inflation.</t>
         </is>
       </c>
     </row>

--- a/engine/egch_study/EGCH_Valuation_Model_03092026.xlsx
+++ b/engine/egch_study/EGCH_Valuation_Model_03092026.xlsx
@@ -1343,23 +1343,23 @@
         </is>
       </c>
       <c r="B7" s="14">
-        <f>B5*'Assumptions'!C143/365</f>
+        <f>B5*'Assumptions'!C144/365</f>
         <v/>
       </c>
       <c r="C7" s="14">
-        <f>C5*'Assumptions'!C143/365</f>
+        <f>C5*'Assumptions'!C144/365</f>
         <v/>
       </c>
       <c r="D7" s="14">
-        <f>D5*'Assumptions'!C143/365</f>
+        <f>D5*'Assumptions'!C144/365</f>
         <v/>
       </c>
       <c r="E7" s="14">
-        <f>E5*'Assumptions'!C143/365</f>
+        <f>E5*'Assumptions'!C144/365</f>
         <v/>
       </c>
       <c r="F7" s="14">
-        <f>F5*'Assumptions'!C143/365</f>
+        <f>F5*'Assumptions'!C144/365</f>
         <v/>
       </c>
     </row>
@@ -1370,23 +1370,23 @@
         </is>
       </c>
       <c r="B8" s="14">
-        <f>B6*'Assumptions'!C144/365</f>
+        <f>B6*'Assumptions'!C145/365</f>
         <v/>
       </c>
       <c r="C8" s="14">
-        <f>C6*'Assumptions'!C144/365</f>
+        <f>C6*'Assumptions'!C145/365</f>
         <v/>
       </c>
       <c r="D8" s="14">
-        <f>D6*'Assumptions'!C144/365</f>
+        <f>D6*'Assumptions'!C145/365</f>
         <v/>
       </c>
       <c r="E8" s="14">
-        <f>E6*'Assumptions'!C144/365</f>
+        <f>E6*'Assumptions'!C145/365</f>
         <v/>
       </c>
       <c r="F8" s="14">
-        <f>F6*'Assumptions'!C144/365</f>
+        <f>F6*'Assumptions'!C145/365</f>
         <v/>
       </c>
     </row>
@@ -1397,23 +1397,23 @@
         </is>
       </c>
       <c r="B9" s="14">
-        <f>B6*'Assumptions'!C145/365</f>
+        <f>B6*'Assumptions'!C146/365</f>
         <v/>
       </c>
       <c r="C9" s="14">
-        <f>C6*'Assumptions'!C145/365</f>
+        <f>C6*'Assumptions'!C146/365</f>
         <v/>
       </c>
       <c r="D9" s="14">
-        <f>D6*'Assumptions'!C145/365</f>
+        <f>D6*'Assumptions'!C146/365</f>
         <v/>
       </c>
       <c r="E9" s="14">
-        <f>E6*'Assumptions'!C145/365</f>
+        <f>E6*'Assumptions'!C146/365</f>
         <v/>
       </c>
       <c r="F9" s="14">
-        <f>F6*'Assumptions'!C145/365</f>
+        <f>F6*'Assumptions'!C146/365</f>
         <v/>
       </c>
     </row>
@@ -2675,19 +2675,19 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>-2.49</v>
+        <v>-2.64</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>-2.63</v>
+        <v>-2.76</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>-2.76</v>
+        <v>-2.87</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>-2.84</v>
+        <v>-2.94</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>-2.92</v>
+        <v>-3.01</v>
       </c>
     </row>
     <row r="7">
@@ -2697,19 +2697,19 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>-0.8</v>
+        <v>-0.42</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>-1.05</v>
+        <v>-0.72</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>-1.29</v>
+        <v>-1</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>-1.44</v>
+        <v>-1.18</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>-1.59</v>
+        <v>-1.36</v>
       </c>
     </row>
     <row r="8">
@@ -2719,19 +2719,19 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.89</v>
+        <v>1.8</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>0.53</v>
+        <v>1.32</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>0.19</v>
+        <v>0.87</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>-0.03</v>
+        <v>0.58</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>-0.25</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="9">
@@ -2741,19 +2741,19 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>2.57</v>
+        <v>4.01</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>2.1</v>
+        <v>3.36</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>1.66</v>
+        <v>2.74</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>1.38</v>
+        <v>2.34</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>1.09</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="10">
@@ -2763,19 +2763,19 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>4.26</v>
+        <v>6.23</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>3.68</v>
+        <v>5.4</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>3.14</v>
+        <v>4.61</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>2.78</v>
+        <v>4.1</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>2.43</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="13" ht="52" customHeight="1">
@@ -2826,16 +2826,16 @@
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>Country risk priced off the sovereign's credit rating</t>
+          <t>Country risk priced off the sovereign's traded default swap</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Priced off the sovereign's traded default swap instead, which is the narrower of the two spreads</t>
+          <t>Priced off the sovereign's credit rating instead, which is the wider of the two spreads and gives a cost of capital 113 basis points higher</t>
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>2.310891559889441</v>
+        <v>2.423743046900326</v>
       </c>
       <c r="D17" s="11">
         <f>C17-$D$15</f>
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>0.5729787587400788</v>
+        <v>1.437646331702388</v>
       </c>
       <c r="D18" s="11">
         <f>C18-$D$15</f>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>2.199529451608678</v>
+        <v>2.368032883797575</v>
       </c>
       <c r="D19" s="11">
         <f>C19-$D$15</f>
@@ -2892,7 +2892,7 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>1.535325976274551</v>
+        <v>2.796330407586523</v>
       </c>
       <c r="D20" s="11">
         <f>C20-$D$15</f>
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>3.498713152528789</v>
+        <v>5.565392223338636</v>
       </c>
       <c r="D21" s="11">
         <f>C21-$D$15</f>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>0.2460834508623395</v>
+        <v>1.225980946860219</v>
       </c>
       <c r="D22" s="11">
         <f>C22-$D$15</f>
@@ -2949,7 +2949,7 @@
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>2.564332955202137</v>
+        <v>4.311438322198129</v>
       </c>
       <c r="D23" s="11">
         <f>C23-$D$15</f>
@@ -2968,7 +2968,7 @@
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>1.403708461239366</v>
+        <v>2.9895329403091</v>
       </c>
       <c r="D24" s="11">
         <f>C24-$D$15</f>
@@ -2978,16 +2978,16 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>Terminal reinvestment of 38.9% of operating profit after tax, from growth over an 18% return on capital</t>
+          <t>Capital maintenance charged at what replacing the plant costs today, on the 4.45-year average age the accounts MEASURE — accumulated depreciation over the year's own charge</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>23.3%, from a 30% return on capital — the rate a newly completed plant earns on incremental capital while it is still filling</t>
+          <t>Half the 22.1-year life the same accounts imply, 11.04 years, which is what has to be assumed where a company does not disclose enough to measure it</t>
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>3.239589266110914</v>
+        <v>1.734786073867607</v>
       </c>
       <c r="D25" s="11">
         <f>C25-$D$15</f>
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="C26" s="12" t="n">
-        <v>2.079574021395053</v>
+        <v>3.689657950674768</v>
       </c>
       <c r="D26" s="11">
         <f>C26-$D$15</f>
@@ -3720,7 +3720,7 @@
         </is>
       </c>
       <c r="B25" s="15" t="n">
-        <v>0.1150130180266282</v>
+        <v>0.1300292595239384</v>
       </c>
     </row>
     <row r="26">
@@ -3805,7 +3805,7 @@
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>6.259070497380644</v>
+        <v>7.880735124887895</v>
       </c>
     </row>
     <row r="37">
@@ -3826,7 +3826,7 @@
         </is>
       </c>
       <c r="B38" s="12" t="n">
-        <v>5.095373540542885</v>
+        <v>5.808994556124265</v>
       </c>
     </row>
     <row r="39">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>2.310891559889441</v>
+        <v>3.896716038959174</v>
       </c>
     </row>
     <row r="24">
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>6.259070497380644</v>
+        <v>7.880735124887895</v>
       </c>
     </row>
     <row r="25">
@@ -4220,7 +4220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D145"/>
+  <dimension ref="A1:D146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6375,98 +6375,97 @@
         </is>
       </c>
     </row>
-    <row r="118" ht="24" customHeight="1">
+    <row r="118" ht="132" customHeight="1">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>Terminal return on invested capital</t>
+          <t>Average age of the fixed-asset base — MEASURED</t>
         </is>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C118" s="15" t="n">
-        <v>0.18</v>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="C118" s="12" t="n">
+        <v>4.454408352548927</v>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>Constructed: terminal return on invested capital, which sets the terminal reinvestment rate as growth divided by return on capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="10" t="inlineStr">
+          <t>DERIVED BY IDENTITY, labelled as derived: accumulated depreciation over the year's own charge. Under straight-line depreciation accumulated equals age times charge, so the ratio is the charge-weighted average age of the base. THE THREE CONDITIONS THAT BREAK THAT IDENTITY ARE CHECKED AND CLEAR HERE. There is no residual value: the policy note writes off cost over the useful life and mentions none. No useful life has been reassessed: the disclosed rates are unchanged from the prior year's identical table. And the base was not assembled by acquisition — it is one plant, built and extended by this company. The corroboration is that only EGP 220mn, 1.3% of the base, is fully depreciated and still in production, so almost nothing is past its accounting life and the gross-over-charge life below reads close to a true weighted life rather than a longer economic cycle. 4.45 years against the 11.04 that half of that life would assume: this plant was rebuilt recently and has another complex still under construction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="84" customHeight="1">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>Replacement cycle the accounts imply</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="n">
+        <v>22.07019266619699</v>
+      </c>
+      <c r="D119" s="9" t="inlineStr">
+        <is>
+          <t>DERIVED BY IDENTITY, labelled as derived: the depreciable gross cost — cost less land, which is never depreciated — over the year's own charge. It is the replacement cycle the accounts themselves run, and it sits inside the disclosed range: note 5-2 gives 3.95% on the urea and ammonia machinery (25.3 years), 9.5% on the factories (10.5), 6.5% on the workshops (15.4), 6% on the factory buildings (16.7), 2 to 5% on the residential city and the water and sewage pipes (20 to 50) and 4.75% on the intangible (21.1). A weighted life cannot be read off the note because it publishes no class balances, so the identity supplies one and the disclosed range is what checks it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="10" t="inlineStr">
         <is>
           <t>CAPITAL, WORKING CAPITAL AND THE PROJECT</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="24" customHeight="1">
-      <c r="A121" s="6" t="inlineStr">
-        <is>
-          <t>Depreciation charge, FY2024/25</t>
-        </is>
-      </c>
-      <c r="B121" s="6" t="inlineStr">
-        <is>
-          <t>EGP m</t>
-        </is>
-      </c>
-      <c r="C121" s="20" t="n">
-        <v>771.213</v>
-      </c>
-      <c r="D121" s="9" t="inlineStr">
-        <is>
-          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 6 fixed-asset register</t>
         </is>
       </c>
     </row>
     <row r="122" ht="24" customHeight="1">
       <c r="A122" s="6" t="inlineStr">
         <is>
+          <t>Depreciation charge, FY2024/25</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>EGP m</t>
+        </is>
+      </c>
+      <c r="C122" s="20" t="n">
+        <v>771.213</v>
+      </c>
+      <c r="D122" s="9" t="inlineStr">
+        <is>
+          <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 6 fixed-asset register</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="24" customHeight="1">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
           <t>Amortisation, FY2024/25</t>
         </is>
       </c>
-      <c r="B122" s="6" t="inlineStr">
+      <c r="B123" s="6" t="inlineStr">
         <is>
           <t>EGP m</t>
         </is>
       </c>
-      <c r="C122" s="20" t="n">
+      <c r="C123" s="20" t="n">
         <v>119.378</v>
       </c>
-      <c r="D122" s="9" t="inlineStr">
+      <c r="D123" s="9" t="inlineStr">
         <is>
           <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 10 usufruct intangible</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="60" customHeight="1">
-      <c r="A123" s="6" t="inlineStr">
-        <is>
-          <t>Project capital expenditure — FY2026/27</t>
-        </is>
-      </c>
-      <c r="B123" s="6" t="inlineStr">
-        <is>
-          <t>EGP m</t>
-        </is>
-      </c>
-      <c r="C123" s="14">
-        <f>'Cash Flow'!B30</f>
-        <v/>
-      </c>
-      <c r="D123" s="9" t="inlineStr">
-        <is>
-          <t>Constructed: project spending path, RE-ANCHORED 9 August 2026 on the observed run rate. The first year is the company's own nine-month actual extended to a full year (EGP 1,949.1m x 4/3 = EGP 2,598.8m); the remaining years complete the EGP 14,688m still to spend against the bank-approved cost. The first issue opened at EGP 3,000m, above anything the company has actually spent in a year.</t>
         </is>
       </c>
     </row>
     <row r="124" ht="60" customHeight="1">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>Project capital expenditure — FY2027/28</t>
+          <t>Project capital expenditure — FY2026/27</t>
         </is>
       </c>
       <c r="B124" s="6" t="inlineStr">
@@ -6474,8 +6473,9 @@
           <t>EGP m</t>
         </is>
       </c>
-      <c r="C124" s="13" t="n">
-        <v>3100</v>
+      <c r="C124" s="14">
+        <f>'Cash Flow'!B30</f>
+        <v/>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
     <row r="125" ht="60" customHeight="1">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>Project capital expenditure — FY2028/29</t>
+          <t>Project capital expenditure — FY2027/28</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="C125" s="13" t="n">
-        <v>3300</v>
+        <v>3100</v>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
     <row r="126" ht="60" customHeight="1">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>Project capital expenditure — FY2029/30</t>
+          <t>Project capital expenditure — FY2028/29</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
@@ -6515,7 +6515,7 @@
         </is>
       </c>
       <c r="C126" s="13" t="n">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
@@ -6526,351 +6526,351 @@
     <row r="127" ht="60" customHeight="1">
       <c r="A127" s="6" t="inlineStr">
         <is>
+          <t>Project capital expenditure — FY2029/30</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>EGP m</t>
+        </is>
+      </c>
+      <c r="C127" s="13" t="n">
+        <v>3200</v>
+      </c>
+      <c r="D127" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: project spending path, RE-ANCHORED 9 August 2026 on the observed run rate. The first year is the company's own nine-month actual extended to a full year (EGP 1,949.1m x 4/3 = EGP 2,598.8m); the remaining years complete the EGP 14,688m still to spend against the bank-approved cost. The first issue opened at EGP 3,000m, above anything the company has actually spent in a year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="60" customHeight="1">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
           <t>Project capital expenditure — FY2030/31</t>
         </is>
       </c>
-      <c r="B127" s="6" t="inlineStr">
+      <c r="B128" s="6" t="inlineStr">
         <is>
           <t>EGP m</t>
         </is>
       </c>
-      <c r="C127" s="14">
-        <f>'Cash Flow'!D34-(C123+C124+C125+C126)</f>
-        <v/>
-      </c>
-      <c r="D127" s="9" t="inlineStr">
+      <c r="C128" s="14">
+        <f>'Cash Flow'!D34-(C124+C125+C126+C127)</f>
+        <v/>
+      </c>
+      <c r="D128" s="9" t="inlineStr">
         <is>
           <t>Constructed: project spending path, RE-ANCHORED 9 August 2026 on the observed run rate. The first year is the company's own nine-month actual extended to a full year (EGP 1,949.1m x 4/3 = EGP 2,598.8m); the remaining years complete the EGP 14,688m still to spend against the bank-approved cost. The first issue opened at EGP 3,000m, above anything the company has actually spent in a year.</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="24" customHeight="1">
-      <c r="A128" s="6" t="inlineStr">
-        <is>
-          <t>Depreciation escalation on the existing base</t>
-        </is>
-      </c>
-      <c r="B128" s="6" t="inlineStr">
-        <is>
-          <t>per year</t>
-        </is>
-      </c>
-      <c r="C128" s="15" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D128" s="9" t="inlineStr">
-        <is>
-          <t>Constructed: escalation on the existing depreciation base, reflecting ordinary additions to the plant already in service</t>
         </is>
       </c>
     </row>
     <row r="129" ht="24" customHeight="1">
       <c r="A129" s="6" t="inlineStr">
         <is>
+          <t>Depreciation escalation on the existing base</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>per year</t>
+        </is>
+      </c>
+      <c r="C129" s="15" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D129" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: escalation on the existing depreciation base, reflecting ordinary additions to the plant already in service</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="24" customHeight="1">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
           <t>Depreciation rate on the new complex</t>
         </is>
       </c>
-      <c r="B129" s="6" t="inlineStr">
+      <c r="B130" s="6" t="inlineStr">
         <is>
           <t>per year</t>
         </is>
       </c>
-      <c r="C129" s="23" t="n">
+      <c r="C130" s="23" t="n">
         <v>0.0395</v>
       </c>
-      <c r="D129" s="9" t="inlineStr">
+      <c r="D130" s="9" t="inlineStr">
         <is>
           <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 5-2 depreciation rates</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="48" customHeight="1">
-      <c r="A130" s="6" t="inlineStr">
+    <row r="131" ht="48" customHeight="1">
+      <c r="A131" s="6" t="inlineStr">
         <is>
           <t>New complex nameplate</t>
         </is>
       </c>
-      <c r="B130" s="6" t="inlineStr">
+      <c r="B131" s="6" t="inlineStr">
         <is>
           <t>tonnes/day</t>
         </is>
       </c>
-      <c r="C130" s="13" t="n">
+      <c r="C131" s="13" t="n">
         <v>800</v>
       </c>
-      <c r="D130" s="9" t="inlineStr">
+      <c r="D131" s="9" t="inlineStr">
         <is>
           <t>EPC award for this plant (Tecnimont S.p.A. with Orascom Construction, announced 9 June 2023): 600 t/day nitric acid converted to 800 t/day of fertilizer-grade granulated ammonium nitrate. FOUND BY EXTERNAL CRITIQUE 9 August 2026 -- the study had said 'no filing states it' and derived the plate from the ammonia surplus instead.</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="24" customHeight="1">
-      <c r="A131" s="6" t="inlineStr">
+    <row r="132" ht="24" customHeight="1">
+      <c r="A132" s="6" t="inlineStr">
         <is>
           <t>Operating days a year</t>
         </is>
       </c>
-      <c r="B131" s="6" t="inlineStr">
+      <c r="B132" s="6" t="inlineStr">
         <is>
           <t>days</t>
         </is>
       </c>
-      <c r="C131" s="13" t="n">
+      <c r="C132" s="13" t="n">
         <v>330</v>
       </c>
-      <c r="D131" s="9" t="inlineStr">
+      <c r="D132" s="9" t="inlineStr">
         <is>
           <t>Constructed: operating days a year for a continuous nitrate line, net of the turnaround the company takes annually</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="48" customHeight="1">
-      <c r="A132" s="6" t="inlineStr">
+    <row r="133" ht="48" customHeight="1">
+      <c r="A133" s="6" t="inlineStr">
         <is>
           <t>Steady-state depreciation wedge in the terminal year</t>
         </is>
       </c>
-      <c r="B132" s="6" t="inlineStr">
+      <c r="B133" s="6" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="C132" s="15" t="n">
+      <c r="C133" s="15" t="n">
         <v>0.025390625</v>
       </c>
-      <c r="D132" s="9" t="inlineStr">
+      <c r="D133" s="9" t="inlineStr">
         <is>
           <t>DERIVED: the steady-state currency depreciation the terminal inflation (5%) implies against long-run US inflation (2.4%) on the relative purchasing-power identity — the same wedge that carries the dollar debt in the terminal year. RE-SET 1 September 2026 from a typed 2.5% so that the terminal currency, the terminal cost of debt and the last explicit year share one number.</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="24" customHeight="1">
-      <c r="A133" s="6" t="inlineStr">
+    <row r="134" ht="24" customHeight="1">
+      <c r="A134" s="6" t="inlineStr">
         <is>
           <t>The complex is completed and in service (1 = yes)</t>
         </is>
       </c>
-      <c r="B133" s="6" t="inlineStr">
+      <c r="B134" s="6" t="inlineStr">
         <is>
           <t>switch</t>
         </is>
       </c>
-      <c r="C133" s="13" t="n">
+      <c r="C134" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="D133" s="9" t="inlineStr">
+      <c r="D134" s="9" t="inlineStr">
         <is>
           <t>Case switch. Zero in the capital-discipline column, where the plant is never finished and therefore never depreciated.</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="36" customHeight="1">
-      <c r="A134" s="6" t="inlineStr">
+    <row r="135" ht="36" customHeight="1">
+      <c r="A135" s="6" t="inlineStr">
         <is>
           <t>Approved cost of the new complex</t>
         </is>
       </c>
-      <c r="B134" s="6" t="inlineStr">
+      <c r="B135" s="6" t="inlineStr">
         <is>
           <t>EGP m</t>
         </is>
       </c>
-      <c r="C134" s="13" t="n">
+      <c r="C135" s="13" t="n">
         <v>20341.668</v>
       </c>
-      <c r="D134" s="9" t="inlineStr">
+      <c r="D135" s="9" t="inlineStr">
         <is>
           <t>Audited financial statements, year ended 30 June 2025 (Central Auditing Organization, report dated 23 September 2025), note 18-3 — bank-approved investment cost, agreement of 25 June 2025; dual-currency tranches at the approval rate</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="72" customHeight="1">
-      <c r="A135" s="6" t="inlineStr">
+    <row r="136" ht="72" customHeight="1">
+      <c r="A136" s="6" t="inlineStr">
         <is>
           <t>Maintenance capital expenditure</t>
         </is>
       </c>
-      <c r="B135" s="6" t="inlineStr">
+      <c r="B136" s="6" t="inlineStr">
         <is>
           <t>% of revenue</t>
         </is>
       </c>
-      <c r="C135" s="8">
+      <c r="C136" s="8">
         <f>'Cash Flow'!D28</f>
         <v/>
       </c>
-      <c r="D135" s="9" t="inlineStr">
+      <c r="D136" s="9" t="inlineStr">
         <is>
           <t>Maintenance capital expenditure as a share of revenue, RE-ANCHORED 9 August 2026 on the company's OWN pre-project cash-flow statements: EGP 123.3m spent across FY2021/22 and FY2022/23 on EGP 11,052.9m of revenue. The first issue of this study used a 3.0% mature-plant standard instead, which is 2.7 times what this company has ever spent to keep its plant running, and which no disclosure supports. The replacement-rate framing (gross fixed assets at the disclosed 3.95% machinery rate, 6.11% of revenue) is carried as the published alternative and as the downside case.</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="36" customHeight="1">
-      <c r="A136" s="6" t="inlineStr">
+    <row r="137" ht="36" customHeight="1">
+      <c r="A137" s="6" t="inlineStr">
         <is>
           <t>Wind-down cost if the programme is stopped</t>
         </is>
       </c>
-      <c r="B136" s="6" t="inlineStr">
+      <c r="B137" s="6" t="inlineStr">
         <is>
           <t>EGP m</t>
         </is>
       </c>
-      <c r="C136" s="13" t="n">
+      <c r="C137" s="13" t="n">
         <v>1000</v>
       </c>
-      <c r="D136" s="9" t="inlineStr">
+      <c r="D137" s="9" t="inlineStr">
         <is>
           <t>Constructed: capital-discipline case only: the cost of stopping the programme in the first forecast year — contract settlement and site preservation. No filing states it; it is the study's estimate and is flagged.</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="24" customHeight="1">
-      <c r="A137" s="6" t="inlineStr">
+    <row r="138" ht="24" customHeight="1">
+      <c r="A138" s="6" t="inlineStr">
         <is>
           <t>Ammonia per tonne of nitrate</t>
         </is>
       </c>
-      <c r="B137" s="6" t="inlineStr">
+      <c r="B138" s="6" t="inlineStr">
         <is>
           <t>tonnes</t>
         </is>
       </c>
-      <c r="C137" s="12" t="n">
+      <c r="C138" s="12" t="n">
         <v>0.43</v>
       </c>
-      <c r="D137" s="9" t="inlineStr">
+      <c r="D138" s="9" t="inlineStr">
         <is>
           <t>Constructed: ammonia per tonne of ammonium nitrate through the nitric-acid route plus direct neutralisation</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="40" customHeight="1">
-      <c r="A138" s="6" t="inlineStr">
-        <is>
-          <t>Project nameplate (derived, not disclosed)</t>
-        </is>
-      </c>
-      <c r="B138" s="6" t="inlineStr">
-        <is>
-          <t>tonnes/year</t>
-        </is>
-      </c>
-      <c r="C138" s="14">
-        <f>'Assumptions'!C130*'Assumptions'!C131</f>
-        <v/>
-      </c>
-      <c r="D138" s="9" t="inlineStr">
-        <is>
-          <t>EPC award for this plant (Tecnimont S.p.A. with Orascom Construction, announced 9 June 2023): 600 t/day nitric acid converted to 800 t/day of fertilizer-grade granulated ammonium nitrate. FOUND BY EXTERNAL CRITIQUE 9 August 2026 -- the study had said 'no filing states it' and derived the plate from the ammonia surplus instead.</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" s="6" t="inlineStr">
         <is>
+          <t>Project nameplate (derived, not disclosed)</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>tonnes/year</t>
+        </is>
+      </c>
+      <c r="C139" s="14">
+        <f>'Assumptions'!C131*'Assumptions'!C132</f>
+        <v/>
+      </c>
+      <c r="D139" s="9" t="inlineStr">
+        <is>
+          <t>EPC award for this plant (Tecnimont S.p.A. with Orascom Construction, announced 9 June 2023): 600 t/day nitric acid converted to 800 t/day of fertilizer-grade granulated ammonium nitrate. FOUND BY EXTERNAL CRITIQUE 9 August 2026 -- the study had said 'no filing states it' and derived the plate from the ammonia surplus instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="40" customHeight="1">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
           <t>Cross-check: nameplate derived from the ammonia surplus</t>
         </is>
       </c>
-      <c r="B139" s="6" t="inlineStr">
+      <c r="B140" s="6" t="inlineStr">
         <is>
           <t>tonnes/year</t>
         </is>
       </c>
-      <c r="C139" s="14">
-        <f>('Assumptions'!C14-'Assumptions'!C13*'Assumptions'!C15)/'Assumptions'!C137</f>
-        <v/>
-      </c>
-      <c r="D139" s="9" t="inlineStr">
+      <c r="C140" s="14">
+        <f>('Assumptions'!C14-'Assumptions'!C13*'Assumptions'!C15)/'Assumptions'!C138</f>
+        <v/>
+      </c>
+      <c r="D140" s="9" t="inlineStr">
         <is>
           <t>The construction the study used before the engineering award was found. Retained as a cross-check on the disclosed plate, not as the plate itself.</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="14" customHeight="1">
-      <c r="A140" s="6" t="inlineStr">
-        <is>
-          <t>Project utilisation in the terminal year</t>
-        </is>
-      </c>
-      <c r="B140" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C140" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D140" s="9" t="inlineStr">
-        <is>
-          <t>Constructed: project utilisation in the terminal year, central case</t>
         </is>
       </c>
     </row>
     <row r="141" ht="14" customHeight="1">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>Nitrate price</t>
+          <t>Project utilisation in the terminal year</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>US$/tonne</t>
-        </is>
-      </c>
-      <c r="C141" s="13" t="n">
-        <v>280</v>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C141" s="15" t="n">
+        <v>0.5</v>
       </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
-          <t>Mid-cycle ammonium nitrate pricing</t>
+          <t>Constructed: project utilisation in the terminal year, central case</t>
         </is>
       </c>
     </row>
     <row r="142" ht="14" customHeight="1">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>Project cash margin</t>
+          <t>Nitrate price</t>
         </is>
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>% of revenue</t>
-        </is>
-      </c>
-      <c r="C142" s="15" t="n">
-        <v>0.32</v>
+          <t>US$/tonne</t>
+        </is>
+      </c>
+      <c r="C142" s="13" t="n">
+        <v>280</v>
       </c>
       <c r="D142" s="9" t="inlineStr">
         <is>
-          <t>Constructed: conversion margin on ammonium nitrate over its own ammonia feedstock</t>
+          <t>Mid-cycle ammonium nitrate pricing</t>
         </is>
       </c>
     </row>
     <row r="143" ht="14" customHeight="1">
       <c r="A143" s="6" t="inlineStr">
         <is>
-          <t>Days sales outstanding</t>
+          <t>Project cash margin</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>days</t>
-        </is>
-      </c>
-      <c r="C143" s="20" t="n">
-        <v>26.77469536556713</v>
+          <t>% of revenue</t>
+        </is>
+      </c>
+      <c r="C143" s="15" t="n">
+        <v>0.32</v>
       </c>
       <c r="D143" s="9" t="inlineStr">
         <is>
-          <t>Constructed: FY2024/25 receivables over revenue</t>
+          <t>Constructed: conversion margin on ammonium nitrate over its own ammonia feedstock</t>
         </is>
       </c>
     </row>
     <row r="144" ht="14" customHeight="1">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>Days inventory outstanding</t>
+          <t>Days sales outstanding</t>
         </is>
       </c>
       <c r="B144" s="6" t="inlineStr">
@@ -6879,29 +6879,49 @@
         </is>
       </c>
       <c r="C144" s="20" t="n">
-        <v>165.2475279747788</v>
+        <v>26.77469536556713</v>
       </c>
       <c r="D144" s="9" t="inlineStr">
         <is>
-          <t>Constructed: FY2024/25 inventory over cost of sales</t>
+          <t>Constructed: FY2024/25 receivables over revenue</t>
         </is>
       </c>
     </row>
     <row r="145" ht="14" customHeight="1">
       <c r="A145" s="6" t="inlineStr">
         <is>
+          <t>Days inventory outstanding</t>
+        </is>
+      </c>
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="C145" s="20" t="n">
+        <v>165.2475279747788</v>
+      </c>
+      <c r="D145" s="9" t="inlineStr">
+        <is>
+          <t>Constructed: FY2024/25 inventory over cost of sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="14" customHeight="1">
+      <c r="A146" s="6" t="inlineStr">
+        <is>
           <t>Days payable outstanding</t>
         </is>
       </c>
-      <c r="B145" s="6" t="inlineStr">
+      <c r="B146" s="6" t="inlineStr">
         <is>
           <t>days</t>
         </is>
       </c>
-      <c r="C145" s="20" t="n">
+      <c r="C146" s="20" t="n">
         <v>83.17161071710899</v>
       </c>
-      <c r="D145" s="9" t="inlineStr">
+      <c r="D146" s="9" t="inlineStr">
         <is>
           <t>Constructed: FY2024/25 payables over cost of sales</t>
         </is>
@@ -7746,23 +7766,23 @@
         </is>
       </c>
       <c r="B25" s="14">
-        <f>'Assumptions'!C121*(1+'Assumptions'!C128*0)+'Assumptions'!C122</f>
+        <f>'Assumptions'!C122*(1+'Assumptions'!C129*0)+'Assumptions'!C123</f>
         <v/>
       </c>
       <c r="C25" s="14">
-        <f>'Assumptions'!C121*(1+'Assumptions'!C128*1)+'Assumptions'!C122+SUM('Assumptions'!C123:C123)*'Assumptions'!C129</f>
+        <f>'Assumptions'!C122*(1+'Assumptions'!C129*1)+'Assumptions'!C123+SUM('Assumptions'!C124:C124)*'Assumptions'!C130</f>
         <v/>
       </c>
       <c r="D25" s="14">
-        <f>'Assumptions'!C121*(1+'Assumptions'!C128*2)+'Assumptions'!C122+SUM('Assumptions'!C123:C124)*'Assumptions'!C129</f>
+        <f>'Assumptions'!C122*(1+'Assumptions'!C129*2)+'Assumptions'!C123+SUM('Assumptions'!C124:C125)*'Assumptions'!C130</f>
         <v/>
       </c>
       <c r="E25" s="14">
-        <f>'Assumptions'!C121*(1+'Assumptions'!C128*3)+'Assumptions'!C122+SUM('Assumptions'!C123:C125)*'Assumptions'!C129</f>
+        <f>'Assumptions'!C122*(1+'Assumptions'!C129*3)+'Assumptions'!C123+SUM('Assumptions'!C124:C126)*'Assumptions'!C130</f>
         <v/>
       </c>
       <c r="F25" s="14">
-        <f>'Assumptions'!C121*(1+'Assumptions'!C128*4)+'Assumptions'!C122+SUM('Assumptions'!C123:C126)*'Assumptions'!C129</f>
+        <f>'Assumptions'!C122*(1+'Assumptions'!C129*4)+'Assumptions'!C123+SUM('Assumptions'!C124:C127)*'Assumptions'!C130</f>
         <v/>
       </c>
     </row>
@@ -8417,7 +8437,7 @@
         </is>
       </c>
       <c r="B30" s="14">
-        <f>(B29-'Assumptions'!C121-'Assumptions'!C122)*(1-'Assumptions'!C107)</f>
+        <f>(B29-'Assumptions'!C122-'Assumptions'!C123)*(1-'Assumptions'!C107)</f>
         <v/>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -8753,23 +8773,23 @@
         </is>
       </c>
       <c r="B12" s="14">
-        <f>-($I$5*'Assumptions'!C123+$I$6*(1-$I$5)+B5*'Assumptions'!C135)</f>
+        <f>-($I$5*'Assumptions'!C124+$I$6*(1-$I$5)+B5*'Assumptions'!C136)</f>
         <v/>
       </c>
       <c r="C12" s="14">
-        <f>-($I$5*'Assumptions'!C124+C5*'Assumptions'!C135)</f>
+        <f>-($I$5*'Assumptions'!C125+C5*'Assumptions'!C136)</f>
         <v/>
       </c>
       <c r="D12" s="14">
-        <f>-($I$5*'Assumptions'!C125+D5*'Assumptions'!C135)</f>
+        <f>-($I$5*'Assumptions'!C126+D5*'Assumptions'!C136)</f>
         <v/>
       </c>
       <c r="E12" s="14">
-        <f>-($I$5*'Assumptions'!C126+E5*'Assumptions'!C135)</f>
+        <f>-($I$5*'Assumptions'!C127+E5*'Assumptions'!C136)</f>
         <v/>
       </c>
       <c r="F12" s="14">
-        <f>-($I$5*'Assumptions'!C127+F5*'Assumptions'!C135)</f>
+        <f>-($I$5*'Assumptions'!C128+F5*'Assumptions'!C136)</f>
         <v/>
       </c>
     </row>
@@ -8932,15 +8952,15 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Year-five EBIT grown at terminal growth</t>
+          <t>Year-five profit before interest and tax, the project's own depreciation added back, grown at terminal growth</t>
         </is>
       </c>
       <c r="B21" s="14">
-        <f>F9*(1+'Assumptions'!C117)</f>
+        <f>(F9+SUM('Assumptions'!C124:C127)*'Assumptions'!C130)*(1+'Assumptions'!C117)</f>
         <v/>
       </c>
       <c r="D21" s="14">
-        <f>(F9+SUM('Assumptions'!C123:C126)*'Assumptions'!C129)*(1+'Assumptions'!C117)</f>
+        <f>(F9+SUM('Assumptions'!C124:C127)*'Assumptions'!C130)*(1+'Assumptions'!C117)</f>
         <v/>
       </c>
     </row>
@@ -8951,11 +8971,11 @@
         </is>
       </c>
       <c r="B22" s="14">
-        <f>'Assumptions'!C138*'Assumptions'!C140*'Assumptions'!C141*('Assumptions'!C49*(1+'Assumptions'!C117-'Assumptions'!C132))/1000000</f>
+        <f>'Assumptions'!C139*'Assumptions'!C141*'Assumptions'!C142*('Assumptions'!C49*(1+'Assumptions'!C117-'Assumptions'!C133))/1000000</f>
         <v/>
       </c>
       <c r="D22" s="14">
-        <f>'Assumptions'!C138*0*'Assumptions'!C141*('Assumptions'!C49*(1+'Assumptions'!C117-'Assumptions'!C132))/1000000</f>
+        <f>'Assumptions'!C139*0*'Assumptions'!C142*('Assumptions'!C49*(1+'Assumptions'!C117-'Assumptions'!C133))/1000000</f>
         <v/>
       </c>
     </row>
@@ -8966,11 +8986,11 @@
         </is>
       </c>
       <c r="B23" s="14">
-        <f>B22*'Assumptions'!C142-'Assumptions'!C133*'Assumptions'!C134*'Assumptions'!C129</f>
+        <f>B22*'Assumptions'!C143-'Assumptions'!C134*'Assumptions'!C135*'Assumptions'!C130</f>
         <v/>
       </c>
       <c r="D23" s="14">
-        <f>D22*'Assumptions'!C142-0*'Assumptions'!C134*'Assumptions'!C129</f>
+        <f>D22*'Assumptions'!C143-0*'Assumptions'!C135*'Assumptions'!C130</f>
         <v/>
       </c>
     </row>
@@ -8992,7 +9012,7 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Terminal NOPAT</t>
+          <t>Terminal profit after tax</t>
         </is>
       </c>
       <c r="B25" s="14">
@@ -9007,45 +9027,105 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Reinvestment rate = growth / return on capital</t>
-        </is>
-      </c>
-      <c r="B26" s="8">
-        <f>'Assumptions'!C117/'Assumptions'!C118</f>
-        <v/>
-      </c>
-      <c r="D26" s="8">
-        <f>'Assumptions'!C117/'Assumptions'!C118</f>
+          <t>Plus book depreciation and amortisation in the terminal year</t>
+        </is>
+      </c>
+      <c r="B26" s="14">
+        <f>(F8-SUM('Assumptions'!C124:C127)*'Assumptions'!C130)*(1+'Assumptions'!C117)+'Assumptions'!C134*'Assumptions'!C135*'Assumptions'!C130</f>
+        <v/>
+      </c>
+      <c r="D26" s="14">
+        <f>(F8-SUM('Assumptions'!C124:C127)*'Assumptions'!C130)*(1+'Assumptions'!C117)+0*'Assumptions'!C135*'Assumptions'!C130</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Terminal free cash flow</t>
+          <t>Less capital maintenance at replacement cost — the book charge escalated over the measured average age of the base</t>
         </is>
       </c>
       <c r="B27" s="14">
-        <f>B25*(1-B26)</f>
+        <f>-B26*(1+'Assumptions'!C111)^'Assumptions'!C118</f>
         <v/>
       </c>
       <c r="D27" s="14">
-        <f>D25*(1-D26)</f>
+        <f>-D26*(1+'Assumptions'!C111)^'Assumptions'!C118</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
+          <t>Less capital for REAL growth — the stated real growth is zero, so none</t>
+        </is>
+      </c>
+      <c r="B28" s="14">
+        <f>-((1+'Assumptions'!C117)/(1+'Assumptions'!C111)-1)*(-B27*'Assumptions'!C119)</f>
+        <v/>
+      </c>
+      <c r="D28" s="14">
+        <f>-((1+'Assumptions'!C117)/(1+'Assumptions'!C111)-1)*(-D27*'Assumptions'!C119)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Less inflation on the working capital the business carries</t>
+        </is>
+      </c>
+      <c r="B29" s="14">
+        <f>-'Assumptions'!C111*'Cash Flow'!F10*(1+'Assumptions'!C117)</f>
+        <v/>
+      </c>
+      <c r="D29" s="14">
+        <f>-'Assumptions'!C111*'Cash Flow'!F10*(1+'Assumptions'!C117)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Terminal free cash flow</t>
+        </is>
+      </c>
+      <c r="B30" s="14">
+        <f>SUM(B25:B29)</f>
+        <v/>
+      </c>
+      <c r="D30" s="14">
+        <f>SUM(D25:D29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
           <t>TERMINAL VALUE</t>
         </is>
       </c>
-      <c r="B28" s="14">
-        <f>B27/('Assumptions'!C116-'Assumptions'!C117)</f>
-        <v/>
-      </c>
-      <c r="D28" s="14">
-        <f>D27/('Assumptions'!C116-'Assumptions'!C117)</f>
+      <c r="B31" s="14">
+        <f>B30/('Assumptions'!C116-'Assumptions'!C117)</f>
+        <v/>
+      </c>
+      <c r="D31" s="14">
+        <f>D30/('Assumptions'!C116-'Assumptions'!C117)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Memo — the no-growth perpetuity at book depreciation (a diagnostic, not a bound)</t>
+        </is>
+      </c>
+      <c r="B32" s="14">
+        <f>B25/'Assumptions'!C116</f>
+        <v/>
+      </c>
+      <c r="D32" s="14">
+        <f>D25/'Assumptions'!C116</f>
         <v/>
       </c>
     </row>
@@ -9056,11 +9136,11 @@
         </is>
       </c>
       <c r="B33" s="14">
-        <f>B28*F16</f>
+        <f>B31*F16</f>
         <v/>
       </c>
       <c r="D33" s="14">
-        <f>D28*F16</f>
+        <f>D31*F16</f>
         <v/>
       </c>
     </row>
@@ -9275,23 +9355,23 @@
         </is>
       </c>
       <c r="B50" s="14">
-        <f>+'Assumptions'!C123</f>
+        <f>+'Assumptions'!C124</f>
         <v/>
       </c>
       <c r="C50" s="14">
-        <f>+'Assumptions'!C124</f>
+        <f>+'Assumptions'!C125</f>
         <v/>
       </c>
       <c r="D50" s="14">
-        <f>+'Assumptions'!C125</f>
+        <f>+'Assumptions'!C126</f>
         <v/>
       </c>
       <c r="E50" s="14">
-        <f>+'Assumptions'!C126</f>
+        <f>+'Assumptions'!C127</f>
         <v/>
       </c>
       <c r="F50" s="14">
-        <f>+'Assumptions'!C127</f>
+        <f>+'Assumptions'!C128</f>
         <v/>
       </c>
     </row>
@@ -9302,7 +9382,7 @@
         </is>
       </c>
       <c r="B51" s="14">
-        <f>-'Assumptions'!C136</f>
+        <f>-'Assumptions'!C137</f>
         <v/>
       </c>
       <c r="C51" s="14">
@@ -9333,19 +9413,19 @@
         <v/>
       </c>
       <c r="C52" s="14">
-        <f>-SUM('Assumptions'!C123:C123)*'Assumptions'!C129*'Assumptions'!C107</f>
+        <f>-SUM('Assumptions'!C124:C124)*'Assumptions'!C130*'Assumptions'!C107</f>
         <v/>
       </c>
       <c r="D52" s="14">
-        <f>-SUM('Assumptions'!C123:C124)*'Assumptions'!C129*'Assumptions'!C107</f>
+        <f>-SUM('Assumptions'!C124:C125)*'Assumptions'!C130*'Assumptions'!C107</f>
         <v/>
       </c>
       <c r="E52" s="14">
-        <f>-SUM('Assumptions'!C123:C125)*'Assumptions'!C129*'Assumptions'!C107</f>
+        <f>-SUM('Assumptions'!C124:C126)*'Assumptions'!C130*'Assumptions'!C107</f>
         <v/>
       </c>
       <c r="F52" s="14">
-        <f>-SUM('Assumptions'!C123:C126)*'Assumptions'!C129*'Assumptions'!C107</f>
+        <f>-SUM('Assumptions'!C124:C127)*'Assumptions'!C130*'Assumptions'!C107</f>
         <v/>
       </c>
     </row>
